--- a/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
+++ b/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -88,66 +88,36 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
   </si>
   <si>
     <t>ELIZALDE</t>
   </si>
   <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>YOLET</t>
   </si>
   <si>
@@ -157,37 +127,13 @@
     <t>ARACELY</t>
   </si>
   <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>CELINA MONSERRAT</t>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
   </si>
   <si>
     <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>LESLIE YAMILET</t>
-  </si>
-  <si>
-    <t>JOSE MARCELO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
   </si>
   <si>
     <t>AZUL MARIAM</t>
@@ -812,16 +758,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -835,16 +784,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H3">
+        <v>5.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -858,16 +810,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>72.22</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -881,16 +836,19 @@
         <v>18</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>72.22</v>
+      </c>
+      <c r="H5">
+        <v>5.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -904,16 +862,19 @@
         <v>23</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>23</v>
       </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -927,16 +888,19 @@
         <v>25</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>25</v>
       </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -950,16 +914,19 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="H8">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -1015,16 +982,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1041,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
         <v>12</v>
       </c>
-      <c r="F3">
-        <v>8</v>
-      </c>
       <c r="G3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1067,16 +1034,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>61.11</v>
+        <v>72.22</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1093,16 +1060,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>55.56</v>
+        <v>72.22</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1128,7 +1095,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1145,16 +1112,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G7">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1171,16 +1138,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G8">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="H8">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1228,10 +1195,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1251,10 +1218,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1274,10 +1241,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1297,10 +1264,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1320,10 +1287,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1337,19 +1304,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920413</v>
+        <v>22330051920201</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
@@ -1360,323 +1327,70 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920413</v>
+        <v>22330051920412</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920180</v>
+        <v>22330051920298</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920180</v>
+        <v>22330051920397</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920264</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920264</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920271</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920297</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920415</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920298</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920417</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920306</v>
-      </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920308</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920370</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920397</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
+++ b/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -79,15 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>COBOS</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -100,15 +94,9 @@
     <t>SANTOS</t>
   </si>
   <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -118,13 +106,7 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>YOLET</t>
-  </si>
-  <si>
     <t>DAVID</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
   </si>
   <si>
     <t>ALEXANDER</t>
@@ -1157,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1189,19 +1171,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920007</v>
+        <v>22330051920188</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -1212,16 +1194,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920007</v>
+        <v>22330051920201</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1235,162 +1217,70 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920188</v>
+        <v>22330051920412</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920190</v>
+        <v>22330051920298</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920190</v>
+        <v>22330051920397</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920201</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920412</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920298</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920397</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
+++ b/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="61">
   <si>
     <t>Mat</t>
   </si>
@@ -79,9 +79,36 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -94,6 +121,33 @@
     <t>SANTOS</t>
   </si>
   <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -103,7 +157,34 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
   </si>
   <si>
     <t>DAVID</t>
@@ -1139,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1171,116 +1252,553 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920188</v>
+        <v>21330051920396</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920201</v>
+        <v>21330051920396</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920412</v>
+        <v>22330051920405</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920298</v>
+        <v>22330051920405</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
+        <v>22330051920279</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920279</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920133</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920133</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920177</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920177</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920007</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920007</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920190</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920190</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920359</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920193</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920193</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920395</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920395</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920188</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920201</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920412</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920298</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
         <v>22330051920397</v>
       </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="B25" t="s">
         <v>33</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
         <v>13</v>
       </c>
-      <c r="G6">
+      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
+++ b/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -79,127 +79,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ARIAS</t>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>GAMALIEL</t>
+  </si>
+  <si>
+    <t>MOISES ALBERTO</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
@@ -597,10 +510,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -609,7 +522,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -623,10 +536,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -635,7 +548,7 @@
         <v>8</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="H3">
         <v>5.3</v>
@@ -701,10 +614,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -713,7 +626,7 @@
         <v>23</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="H6">
         <v>8.300000000000001</v>
@@ -727,10 +640,10 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -739,7 +652,7 @@
         <v>22</v>
       </c>
       <c r="G7">
-        <v>88</v>
+        <v>75.86</v>
       </c>
       <c r="H7">
         <v>7.2</v>
@@ -753,10 +666,10 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8">
         <v>9</v>
@@ -765,7 +678,7 @@
         <v>16</v>
       </c>
       <c r="G8">
-        <v>64</v>
+        <v>55.17</v>
       </c>
       <c r="H8">
         <v>6.1</v>
@@ -818,10 +731,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -830,7 +743,7 @@
         <v>15</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -844,10 +757,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -856,7 +769,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="H3">
         <v>5.3</v>
@@ -922,10 +835,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -934,7 +847,7 @@
         <v>23</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="H6">
         <v>8.300000000000001</v>
@@ -948,10 +861,10 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -960,7 +873,7 @@
         <v>25</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H7">
         <v>7.2</v>
@@ -974,10 +887,10 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -986,7 +899,7 @@
         <v>22</v>
       </c>
       <c r="G8">
-        <v>88</v>
+        <v>75.86</v>
       </c>
       <c r="H8">
         <v>6.1</v>
@@ -1039,22 +952,22 @@
         <v>10</v>
       </c>
       <c r="C2">
+        <v>21</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>20</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
       <c r="G2">
-        <v>75</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1065,22 +978,22 @@
         <v>10</v>
       </c>
       <c r="C3">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>20</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>8</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
       <c r="G3">
-        <v>60</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1097,16 +1010,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>72.22</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1123,16 +1036,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>72.22</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1143,10 +1056,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1155,10 +1068,10 @@
         <v>23</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1169,22 +1082,22 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>25</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1195,22 +1108,22 @@
         <v>13</v>
       </c>
       <c r="C8">
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>25</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>22</v>
-      </c>
       <c r="G8">
-        <v>88</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -1220,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1252,22 +1165,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920396</v>
+        <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1275,22 +1188,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920396</v>
+        <v>22330051920291</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1298,22 +1211,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920405</v>
+        <v>22330051920305</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1321,22 +1234,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920405</v>
+        <v>22330051920305</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1344,22 +1257,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920279</v>
+        <v>22330051920309</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1367,22 +1280,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920279</v>
+        <v>22330051920309</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1390,22 +1303,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920133</v>
+        <v>22330051920315</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -1413,393 +1326,25 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920133</v>
+        <v>22330051920315</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920177</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920177</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920007</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920007</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920190</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920190</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920359</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920193</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920193</v>
-      </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920395</v>
-      </c>
-      <c r="B19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920395</v>
-      </c>
-      <c r="B20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920188</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920201</v>
-      </c>
-      <c r="B22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920412</v>
-      </c>
-      <c r="B23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920298</v>
-      </c>
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920397</v>
-      </c>
-      <c r="B25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
+++ b/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -91,6 +94,9 @@
     <t>VENTURA</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
@@ -101,6 +107,9 @@
   </si>
   <si>
     <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
   </si>
   <si>
     <t>EFRAIN DE JESUS</t>
@@ -1133,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1165,22 +1174,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920291</v>
+        <v>22330051920225</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1191,16 +1200,16 @@
         <v>22330051920291</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
@@ -1211,19 +1220,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920305</v>
+        <v>22330051920291</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
@@ -1237,16 +1246,16 @@
         <v>22330051920305</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -1257,19 +1266,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920309</v>
+        <v>22330051920305</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -1283,16 +1292,16 @@
         <v>22330051920309</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
@@ -1303,19 +1312,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920315</v>
+        <v>22330051920309</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
@@ -1329,21 +1338,44 @@
         <v>22330051920315</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920315</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
         <v>9</v>
       </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
         <v>4</v>
       </c>
     </row>

--- a/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
+++ b/docentes/Morales Estrada Adilene - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,51 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>MOISES ALBERTO</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
@@ -522,19 +477,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>47.62</v>
+        <v>52.38</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -548,19 +503,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>12</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>38.1</v>
+        <v>42.86</v>
       </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -626,16 +581,16 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>8.300000000000001</v>
@@ -652,19 +607,19 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>75.86</v>
+        <v>89.66</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -678,19 +633,19 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>9</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G8">
-        <v>55.17</v>
+        <v>68.97</v>
       </c>
       <c r="H8">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -743,19 +698,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>71.43000000000001</v>
+        <v>76.19</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -769,19 +724,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -847,16 +802,16 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>8.300000000000001</v>
@@ -873,19 +828,19 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>86.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -899,19 +854,19 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G8">
-        <v>75.86</v>
+        <v>89.66</v>
       </c>
       <c r="H8">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -964,19 +919,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -990,19 +945,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1068,16 +1023,16 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>8.5</v>
@@ -1097,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>86.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1120,19 +1075,19 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>86.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1142,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1172,213 +1127,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920225</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920291</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920291</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920305</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920305</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920309</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920309</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920315</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920315</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
